--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/100.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/100.xlsx
@@ -426,13 +426,13 @@
         <v>-21.70846759590105</v>
       </c>
       <c r="E2">
-        <v>-20.43500683098085</v>
+        <v>-19.17083575508424</v>
       </c>
       <c r="F2">
-        <v>-3.72160720617225</v>
+        <v>-2.795050101649307</v>
       </c>
       <c r="G2">
-        <v>-13.97136780623857</v>
+        <v>-14.75509375190635</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.91669190565841</v>
       </c>
       <c r="E3">
-        <v>-19.90721673582163</v>
+        <v>-20.57143566979014</v>
       </c>
       <c r="F3">
-        <v>-3.442034036094819</v>
+        <v>-2.591163204430862</v>
       </c>
       <c r="G3">
-        <v>-13.32670839270563</v>
+        <v>-14.64952698899239</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.14491238048996</v>
       </c>
       <c r="E4">
-        <v>-20.15401716558825</v>
+        <v>-20.89554397515711</v>
       </c>
       <c r="F4">
-        <v>-3.573071818808867</v>
+        <v>-2.662918873963564</v>
       </c>
       <c r="G4">
-        <v>-12.66255063319396</v>
+        <v>-14.07426899892501</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.32080532778678</v>
       </c>
       <c r="E5">
-        <v>-20.8726763936026</v>
+        <v>-20.78947095792099</v>
       </c>
       <c r="F5">
-        <v>-2.839072858903684</v>
+        <v>-2.685317928535262</v>
       </c>
       <c r="G5">
-        <v>-12.68310502535979</v>
+        <v>-14.10745025730576</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-22.42458155112568</v>
       </c>
       <c r="E6">
-        <v>-20.60609006508451</v>
+        <v>-21.32685912445188</v>
       </c>
       <c r="F6">
-        <v>-3.620601883646697</v>
+        <v>-2.737692285944664</v>
       </c>
       <c r="G6">
-        <v>-13.35737680941744</v>
+        <v>-13.4484891849027</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.44229422791205</v>
       </c>
       <c r="E7">
-        <v>-22.6532245399378</v>
+        <v>-23.16785726161995</v>
       </c>
       <c r="F7">
-        <v>-3.691126599218839</v>
+        <v>-2.489519210637752</v>
       </c>
       <c r="G7">
-        <v>-12.77903552998795</v>
+        <v>-13.85054385193414</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.33692785329703</v>
       </c>
       <c r="E8">
-        <v>-21.80212355598598</v>
+        <v>-22.83481124548195</v>
       </c>
       <c r="F8">
-        <v>-3.116542804145407</v>
+        <v>-2.431511126521911</v>
       </c>
       <c r="G8">
-        <v>-12.67614216953529</v>
+        <v>-13.08762423528525</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-22.12107495649045</v>
       </c>
       <c r="E9">
-        <v>-20.60163366933297</v>
+        <v>-23.03582667360365</v>
       </c>
       <c r="F9">
-        <v>-3.485052812057003</v>
+        <v>-2.491925617942884</v>
       </c>
       <c r="G9">
-        <v>-12.21571125344655</v>
+        <v>-13.1491842873714</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.79328847293287</v>
       </c>
       <c r="E10">
-        <v>-23.26629252322971</v>
+        <v>-23.87282335189635</v>
       </c>
       <c r="F10">
-        <v>-3.707632648087022</v>
+        <v>-2.651402910329845</v>
       </c>
       <c r="G10">
-        <v>-12.14700298266993</v>
+        <v>-12.63709848417519</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-21.3702479952472</v>
       </c>
       <c r="E11">
-        <v>-23.01257284339594</v>
+        <v>-24.97754018539882</v>
       </c>
       <c r="F11">
-        <v>-3.171911709715928</v>
+        <v>-1.97900052212943</v>
       </c>
       <c r="G11">
-        <v>-11.3535089361145</v>
+        <v>-12.03110811415352</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.89874511371913</v>
       </c>
       <c r="E12">
-        <v>-26.10987587421139</v>
+        <v>-24.907782847987</v>
       </c>
       <c r="F12">
-        <v>-2.646528796531773</v>
+        <v>-2.250976734755787</v>
       </c>
       <c r="G12">
-        <v>-10.40829538376342</v>
+        <v>-11.89818205329699</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-20.38766440865493</v>
       </c>
       <c r="E13">
-        <v>-27.51525198194085</v>
+        <v>-25.85063657652692</v>
       </c>
       <c r="F13">
-        <v>-3.023161775195221</v>
+        <v>-2.07862329945971</v>
       </c>
       <c r="G13">
-        <v>-10.82740212909172</v>
+        <v>-10.9940107112905</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.87914452251689</v>
       </c>
       <c r="E14">
-        <v>-27.193037540938</v>
+        <v>-26.70753959669952</v>
       </c>
       <c r="F14">
-        <v>-2.913691366180461</v>
+        <v>-1.926607940637167</v>
       </c>
       <c r="G14">
-        <v>-9.380567943237898</v>
+        <v>-10.86266937240077</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.37719088318311</v>
       </c>
       <c r="E15">
-        <v>-25.93709397667588</v>
+        <v>-28.57405298764168</v>
       </c>
       <c r="F15">
-        <v>-2.806386309556618</v>
+        <v>-1.639131317169627</v>
       </c>
       <c r="G15">
-        <v>-8.881118143862675</v>
+        <v>-10.32393047767389</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-18.87906251976513</v>
       </c>
       <c r="E16">
-        <v>-28.14468777106391</v>
+        <v>-28.86448082576995</v>
       </c>
       <c r="F16">
-        <v>-2.588098245040504</v>
+        <v>-1.690318624090817</v>
       </c>
       <c r="G16">
-        <v>-10.43564423872762</v>
+        <v>-10.3221930271485</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.40350602114781</v>
       </c>
       <c r="E17">
-        <v>-28.20340171956302</v>
+        <v>-30.49148059621491</v>
       </c>
       <c r="F17">
-        <v>-2.005763416179076</v>
+        <v>-1.41301600906446</v>
       </c>
       <c r="G17">
-        <v>-8.416132783834739</v>
+        <v>-9.600067600108042</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-17.93450546453786</v>
       </c>
       <c r="E18">
-        <v>-28.14622653585976</v>
+        <v>-30.05864121836393</v>
       </c>
       <c r="F18">
-        <v>-2.189884638799323</v>
+        <v>-1.072412870585776</v>
       </c>
       <c r="G18">
-        <v>-9.343633739507418</v>
+        <v>-9.754162883481618</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.49376593488213</v>
       </c>
       <c r="E19">
-        <v>-31.30159353760199</v>
+        <v>-30.69270368490285</v>
       </c>
       <c r="F19">
-        <v>-1.762934138987624</v>
+        <v>-0.9644674859595693</v>
       </c>
       <c r="G19">
-        <v>-7.741252696287363</v>
+        <v>-10.09766377082357</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.07818351269275</v>
       </c>
       <c r="E20">
-        <v>-30.73623349279838</v>
+        <v>-30.8580637938009</v>
       </c>
       <c r="F20">
-        <v>-1.474902509360208</v>
+        <v>-0.9407198492561131</v>
       </c>
       <c r="G20">
-        <v>-9.258498663763509</v>
+        <v>-9.32600338128363</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-16.67684901856951</v>
       </c>
       <c r="E21">
-        <v>-31.80354235189812</v>
+        <v>-32.52183194410456</v>
       </c>
       <c r="F21">
-        <v>-2.183978379217362</v>
+        <v>-0.7201769686695784</v>
       </c>
       <c r="G21">
-        <v>-8.343385691175662</v>
+        <v>-9.43866223187935</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-16.30358681655592</v>
       </c>
       <c r="E22">
-        <v>-32.65773747828693</v>
+        <v>-32.60929442139413</v>
       </c>
       <c r="F22">
-        <v>-2.127929384009142</v>
+        <v>-0.669793178129104</v>
       </c>
       <c r="G22">
-        <v>-8.846716362385575</v>
+        <v>-9.544533146538177</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-15.94132241743147</v>
       </c>
       <c r="E23">
-        <v>-33.41671400523705</v>
+        <v>-33.05890446657477</v>
       </c>
       <c r="F23">
-        <v>-1.095690822971845</v>
+        <v>-0.2100981432521436</v>
       </c>
       <c r="G23">
-        <v>-8.299467745663955</v>
+        <v>-10.00079861963179</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-15.61060447379919</v>
       </c>
       <c r="E24">
-        <v>-32.96913695699992</v>
+        <v>-32.7226355584487</v>
       </c>
       <c r="F24">
-        <v>-1.250100991955881</v>
+        <v>-0.4092558909680063</v>
       </c>
       <c r="G24">
-        <v>-9.912582865270371</v>
+        <v>-10.03940761601747</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-15.31881885150717</v>
       </c>
       <c r="E25">
-        <v>-32.51738385477567</v>
+        <v>-33.50509434222941</v>
       </c>
       <c r="F25">
-        <v>-1.791723219704518</v>
+        <v>-0.04226262377093573</v>
       </c>
       <c r="G25">
-        <v>-9.813126550071912</v>
+        <v>-9.697620682499581</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.06668923241</v>
       </c>
       <c r="E26">
-        <v>-32.18028430438464</v>
+        <v>-33.34187936698063</v>
       </c>
       <c r="F26">
-        <v>-1.358080339645602</v>
+        <v>-0.2545185168598643</v>
       </c>
       <c r="G26">
-        <v>-8.87728557080292</v>
+        <v>-10.4256033150302</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-14.8818616779509</v>
       </c>
       <c r="E27">
-        <v>-33.45582271967731</v>
+        <v>-32.65853281825563</v>
       </c>
       <c r="F27">
-        <v>-1.396979644513664</v>
+        <v>-0.299261125387274</v>
       </c>
       <c r="G27">
-        <v>-9.393468937634884</v>
+        <v>-10.49151547834974</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.75726117357197</v>
       </c>
       <c r="E28">
-        <v>-32.25077053038397</v>
+        <v>-33.53205283693887</v>
       </c>
       <c r="F28">
-        <v>-0.9459087426672492</v>
+        <v>-0.200552037302282</v>
       </c>
       <c r="G28">
-        <v>-9.473254597711602</v>
+        <v>-10.47906092127784</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.71231903692814</v>
       </c>
       <c r="E29">
-        <v>-30.71626900595993</v>
+        <v>-32.74642515291732</v>
       </c>
       <c r="F29">
-        <v>-1.610147570113075</v>
+        <v>-0.2717932906778451</v>
       </c>
       <c r="G29">
-        <v>-9.612706214673622</v>
+        <v>-9.959697667533899</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.75088337119839</v>
       </c>
       <c r="E30">
-        <v>-30.569405223697</v>
+        <v>-32.73662980400771</v>
       </c>
       <c r="F30">
-        <v>-1.873788749932462</v>
+        <v>-0.104190542436824</v>
       </c>
       <c r="G30">
-        <v>-9.142340110043401</v>
+        <v>-10.72647465931617</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.85850504851675</v>
       </c>
       <c r="E31">
-        <v>-31.69340541738065</v>
+        <v>-33.05494853278787</v>
       </c>
       <c r="F31">
-        <v>-1.692947033859899</v>
+        <v>-0.2695931468560097</v>
       </c>
       <c r="G31">
-        <v>-9.872878661528722</v>
+        <v>-10.26625521353931</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.045057629041</v>
       </c>
       <c r="E32">
-        <v>-32.19439068664942</v>
+        <v>-32.71679821993165</v>
       </c>
       <c r="F32">
-        <v>-1.166346420593628</v>
+        <v>-0.1108100263525948</v>
       </c>
       <c r="G32">
-        <v>-9.820906568953429</v>
+        <v>-10.91346401916547</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.28193851361872</v>
       </c>
       <c r="E33">
-        <v>-32.42911980770042</v>
+        <v>-31.65649167512558</v>
       </c>
       <c r="F33">
-        <v>-1.65420843226798</v>
+        <v>-0.277648191480832</v>
       </c>
       <c r="G33">
-        <v>-11.26717813934786</v>
+        <v>-10.57855509227287</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.56214760364562</v>
       </c>
       <c r="E34">
-        <v>-30.64138660577327</v>
+        <v>-32.00091541368794</v>
       </c>
       <c r="F34">
-        <v>-1.161022503295836</v>
+        <v>-0.381930535451859</v>
       </c>
       <c r="G34">
-        <v>-10.47360968657159</v>
+        <v>-10.72870031908009</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.87220252567936</v>
       </c>
       <c r="E35">
-        <v>-30.63005456867348</v>
+        <v>-30.95247874684823</v>
       </c>
       <c r="F35">
-        <v>-1.576058594753069</v>
+        <v>-0.3631017443862262</v>
       </c>
       <c r="G35">
-        <v>-9.60173717127406</v>
+        <v>-11.16409680528464</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.18334216474646</v>
       </c>
       <c r="E36">
-        <v>-30.83827997165508</v>
+        <v>-30.42984278694313</v>
       </c>
       <c r="F36">
-        <v>-1.378216294472852</v>
+        <v>-0.1061678554273064</v>
       </c>
       <c r="G36">
-        <v>-9.951103096339953</v>
+        <v>-10.69015659130919</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-16.50260995542039</v>
       </c>
       <c r="E37">
-        <v>-28.98767130348135</v>
+        <v>-30.42016580455628</v>
       </c>
       <c r="F37">
-        <v>-1.223999135093669</v>
+        <v>-0.3781838296889968</v>
       </c>
       <c r="G37">
-        <v>-10.42946069016357</v>
+        <v>-10.7558429252216</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.80834077041691</v>
       </c>
       <c r="E38">
-        <v>-28.70508680494002</v>
+        <v>-29.66492093798151</v>
       </c>
       <c r="F38">
-        <v>-1.226289570962409</v>
+        <v>0.07425553510684273</v>
       </c>
       <c r="G38">
-        <v>-9.234295756031594</v>
+        <v>-11.27745664080308</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.10252866128248</v>
       </c>
       <c r="E39">
-        <v>-28.28690618646002</v>
+        <v>-30.39260301759905</v>
       </c>
       <c r="F39">
-        <v>-1.50139204216693</v>
+        <v>-0.152067693216427</v>
       </c>
       <c r="G39">
-        <v>-9.481235643926635</v>
+        <v>-11.37162750357683</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.38680585479626</v>
       </c>
       <c r="E40">
-        <v>-27.94672080005464</v>
+        <v>-28.58694247898828</v>
       </c>
       <c r="F40">
-        <v>-0.778810470174533</v>
+        <v>-0.4208604899138246</v>
       </c>
       <c r="G40">
-        <v>-10.78477650215261</v>
+        <v>-11.17177108901022</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.64309336528593</v>
       </c>
       <c r="E41">
-        <v>-28.49156605751926</v>
+        <v>-29.13739249513576</v>
       </c>
       <c r="F41">
-        <v>-1.435347965876532</v>
+        <v>-0.1159376205759238</v>
       </c>
       <c r="G41">
-        <v>-10.08927022696315</v>
+        <v>-11.55402586906266</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.89175466744149</v>
       </c>
       <c r="E42">
-        <v>-27.65624519999613</v>
+        <v>-28.38678676561082</v>
       </c>
       <c r="F42">
-        <v>-1.492584839940366</v>
+        <v>0.001897642472305915</v>
       </c>
       <c r="G42">
-        <v>-11.06415619696453</v>
+        <v>-10.854817558043</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-18.12151266738238</v>
       </c>
       <c r="E43">
-        <v>-26.05017346141699</v>
+        <v>-27.99089850891684</v>
       </c>
       <c r="F43">
-        <v>-0.994175226126168</v>
+        <v>-0.1912792925953444</v>
       </c>
       <c r="G43">
-        <v>-10.55285753326254</v>
+        <v>-11.29781261637999</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.34077001612664</v>
       </c>
       <c r="E44">
-        <v>-26.91956103483202</v>
+        <v>-27.81539210475223</v>
       </c>
       <c r="F44">
-        <v>-1.669030410206272</v>
+        <v>-0.07734066980988359</v>
       </c>
       <c r="G44">
-        <v>-9.851666361725925</v>
+        <v>-11.53300545898731</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-18.56132586665849</v>
       </c>
       <c r="E45">
-        <v>-26.74834489796596</v>
+        <v>-27.07374069884363</v>
       </c>
       <c r="F45">
-        <v>-1.700912614805219</v>
+        <v>0.1695326970420363</v>
       </c>
       <c r="G45">
-        <v>-10.9291141276169</v>
+        <v>-11.69433119950598</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-18.76828118987848</v>
       </c>
       <c r="E46">
-        <v>-25.27332774274178</v>
+        <v>-26.53979554450102</v>
       </c>
       <c r="F46">
-        <v>-1.541856961426284</v>
+        <v>-0.2179444392914605</v>
       </c>
       <c r="G46">
-        <v>-10.44754662331851</v>
+        <v>-11.13372992957311</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-18.98711304395325</v>
       </c>
       <c r="E47">
-        <v>-24.97101964361883</v>
+        <v>-26.22109056706765</v>
       </c>
       <c r="F47">
-        <v>-1.448406349614263</v>
+        <v>-0.2469654628811384</v>
       </c>
       <c r="G47">
-        <v>-10.66614687867702</v>
+        <v>-11.34608658924197</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-19.20799914467562</v>
       </c>
       <c r="E48">
-        <v>-24.49789826912834</v>
+        <v>-25.27211500503493</v>
       </c>
       <c r="F48">
-        <v>-1.60819924998169</v>
+        <v>-0.2455903729924912</v>
       </c>
       <c r="G48">
-        <v>-10.93311900981967</v>
+        <v>-11.58159011045564</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-19.43560296431841</v>
       </c>
       <c r="E49">
-        <v>-26.61922571108837</v>
+        <v>-24.62111158950203</v>
       </c>
       <c r="F49">
-        <v>-1.171651285441156</v>
+        <v>-0.3856523901926372</v>
       </c>
       <c r="G49">
-        <v>-10.96749337847856</v>
+        <v>-12.17872744556884</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-19.67963889426664</v>
       </c>
       <c r="E50">
-        <v>-24.78916713254989</v>
+        <v>-23.24501562161262</v>
       </c>
       <c r="F50">
-        <v>-1.218033233058706</v>
+        <v>-0.3914194840509274</v>
       </c>
       <c r="G50">
-        <v>-9.90249233742572</v>
+        <v>-11.59553018119989</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-19.91626286372502</v>
       </c>
       <c r="E51">
-        <v>-23.58552080529001</v>
+        <v>-23.30026579186681</v>
       </c>
       <c r="F51">
-        <v>-1.144696210154061</v>
+        <v>-0.3881954781192317</v>
       </c>
       <c r="G51">
-        <v>-10.49314588834689</v>
+        <v>-11.50565529865081</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-20.16334596901899</v>
       </c>
       <c r="E52">
-        <v>-22.12484468877046</v>
+        <v>-23.23128095176141</v>
       </c>
       <c r="F52">
-        <v>-1.256789230366084</v>
+        <v>-0.2932446929407411</v>
       </c>
       <c r="G52">
-        <v>-11.40099185336538</v>
+        <v>-11.44329896946437</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-20.40387515591111</v>
       </c>
       <c r="E53">
-        <v>-21.79603494818378</v>
+        <v>-23.01492771421712</v>
       </c>
       <c r="F53">
-        <v>-1.377674542191422</v>
+        <v>-0.4789166193390279</v>
       </c>
       <c r="G53">
-        <v>-12.16562411846604</v>
+        <v>-11.49812199513316</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-20.63277439752454</v>
       </c>
       <c r="E54">
-        <v>-21.40123898606823</v>
+        <v>-21.42024823430197</v>
       </c>
       <c r="F54">
-        <v>-1.23893045752913</v>
+        <v>-0.3901785896815337</v>
       </c>
       <c r="G54">
-        <v>-11.95716007898253</v>
+        <v>-11.74581638821503</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-20.85757770567031</v>
       </c>
       <c r="E55">
-        <v>-22.01697748424201</v>
+        <v>-20.57687637662567</v>
       </c>
       <c r="F55">
-        <v>-1.731598656874524</v>
+        <v>-0.1820943548331035</v>
       </c>
       <c r="G55">
-        <v>-10.9938919224116</v>
+        <v>-12.35810387419046</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-21.05209778449284</v>
       </c>
       <c r="E56">
-        <v>-20.36919919753894</v>
+        <v>-22.52013903624499</v>
       </c>
       <c r="F56">
-        <v>-1.813669985674288</v>
+        <v>-0.3272334358450076</v>
       </c>
       <c r="G56">
-        <v>-11.29030280956365</v>
+        <v>-11.67511481394309</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-21.23738464915552</v>
       </c>
       <c r="E57">
-        <v>-19.20170242165036</v>
+        <v>-20.4893972864908</v>
       </c>
       <c r="F57">
-        <v>-1.311987492251629</v>
+        <v>-0.4950441043041315</v>
       </c>
       <c r="G57">
-        <v>-11.18731546230571</v>
+        <v>-11.97621720912537</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-21.40369019101449</v>
       </c>
       <c r="E58">
-        <v>-20.99198569533095</v>
+        <v>-20.17693873888998</v>
       </c>
       <c r="F58">
-        <v>-0.7763030020462588</v>
+        <v>-0.1091176717486754</v>
       </c>
       <c r="G58">
-        <v>-12.51120446387482</v>
+        <v>-11.94810993285744</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-21.55017435077762</v>
       </c>
       <c r="E59">
-        <v>-20.18078876578809</v>
+        <v>-19.8022277067413</v>
       </c>
       <c r="F59">
-        <v>-1.069239395065651</v>
+        <v>-0.04722123104409357</v>
       </c>
       <c r="G59">
-        <v>-12.47520229596337</v>
+        <v>-12.10146768088403</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-21.6937876932463</v>
       </c>
       <c r="E60">
-        <v>-20.35531085886871</v>
+        <v>-19.79320277853244</v>
       </c>
       <c r="F60">
-        <v>-1.044090989084061</v>
+        <v>-0.3105658553332788</v>
       </c>
       <c r="G60">
-        <v>-11.64930499291534</v>
+        <v>-12.41228335131754</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-21.81255098556994</v>
       </c>
       <c r="E61">
-        <v>-19.41175939082622</v>
+        <v>-19.08718592579087</v>
       </c>
       <c r="F61">
-        <v>-1.489060136641454</v>
+        <v>-0.5571360397157741</v>
       </c>
       <c r="G61">
-        <v>-10.97146171025705</v>
+        <v>-12.20988668226378</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-21.92945411034013</v>
       </c>
       <c r="E62">
-        <v>-19.66804160204741</v>
+        <v>-19.26371401994138</v>
       </c>
       <c r="F62">
-        <v>-0.8944116263374123</v>
+        <v>-0.4217576118110564</v>
       </c>
       <c r="G62">
-        <v>-11.99998542788286</v>
+        <v>-12.0126057672363</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-22.03542543822247</v>
       </c>
       <c r="E63">
-        <v>-20.75775288303327</v>
+        <v>-19.19127370801372</v>
       </c>
       <c r="F63">
-        <v>-1.394889673556401</v>
+        <v>-0.4747201100764457</v>
       </c>
       <c r="G63">
-        <v>-12.34374477893934</v>
+        <v>-12.9425973732489</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-22.12302637198832</v>
       </c>
       <c r="E64">
-        <v>-17.14397725791876</v>
+        <v>-18.95255958069655</v>
       </c>
       <c r="F64">
-        <v>-1.939771527035054</v>
+        <v>-0.4719020041721217</v>
       </c>
       <c r="G64">
-        <v>-11.97345504134797</v>
+        <v>-12.49871857786782</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-22.20563273571388</v>
       </c>
       <c r="E65">
-        <v>-19.52451492508398</v>
+        <v>-18.34761112554467</v>
       </c>
       <c r="F65">
-        <v>-1.754862527014746</v>
+        <v>-0.4915144308008028</v>
       </c>
       <c r="G65">
-        <v>-11.02048366144439</v>
+        <v>-12.74107660900546</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-22.25499549088336</v>
       </c>
       <c r="E66">
-        <v>-19.76080357698746</v>
+        <v>-18.41817003274218</v>
       </c>
       <c r="F66">
-        <v>-1.730163096165473</v>
+        <v>-0.5799451361518584</v>
       </c>
       <c r="G66">
-        <v>-12.01358610183027</v>
+        <v>-12.78226110493027</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-22.2882187230809</v>
       </c>
       <c r="E67">
-        <v>-18.81556175193575</v>
+        <v>-18.02443729272579</v>
       </c>
       <c r="F67">
-        <v>-1.045310345900982</v>
+        <v>-0.7319373006871229</v>
       </c>
       <c r="G67">
-        <v>-12.69524890382535</v>
+        <v>-12.86473713730813</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-22.29689677519745</v>
       </c>
       <c r="E68">
-        <v>-17.91585988906079</v>
+        <v>-18.45204777751881</v>
       </c>
       <c r="F68">
-        <v>-1.740437337062395</v>
+        <v>-0.6770173702489185</v>
       </c>
       <c r="G68">
-        <v>-12.1095244386922</v>
+        <v>-13.07588371685901</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-22.27149395435566</v>
       </c>
       <c r="E69">
-        <v>-17.04299192455555</v>
+        <v>-18.51380602991901</v>
       </c>
       <c r="F69">
-        <v>-1.541958850616828</v>
+        <v>-0.6864566168038189</v>
       </c>
       <c r="G69">
-        <v>-12.2338533176102</v>
+        <v>-12.97759832060967</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.22958534494546</v>
       </c>
       <c r="E70">
-        <v>-17.1121013610007</v>
+        <v>-17.63438845115451</v>
       </c>
       <c r="F70">
-        <v>-2.152030733593594</v>
+        <v>-0.7932149509418136</v>
       </c>
       <c r="G70">
-        <v>-11.23322148982355</v>
+        <v>-12.84389034174809</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.14848967643216</v>
       </c>
       <c r="E71">
-        <v>-17.19496623335368</v>
+        <v>-17.77237889742194</v>
       </c>
       <c r="F71">
-        <v>-0.9312756324967959</v>
+        <v>-1.015097301618675</v>
       </c>
       <c r="G71">
-        <v>-11.13218045265828</v>
+        <v>-12.79896073270733</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-22.046114159681</v>
       </c>
       <c r="E72">
-        <v>-17.86289813824658</v>
+        <v>-18.16204149034001</v>
       </c>
       <c r="F72">
-        <v>-1.934704403632129</v>
+        <v>-0.7731759151006907</v>
       </c>
       <c r="G72">
-        <v>-11.42477051510124</v>
+        <v>-12.98847207183165</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-21.91924236603892</v>
       </c>
       <c r="E73">
-        <v>-19.59304706515498</v>
+        <v>-18.30479151678569</v>
       </c>
       <c r="F73">
-        <v>-1.780160867496243</v>
+        <v>-0.9403156059635469</v>
       </c>
       <c r="G73">
-        <v>-12.09408710592495</v>
+        <v>-12.48530979364787</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-21.75737300881789</v>
       </c>
       <c r="E74">
-        <v>-19.10564695012973</v>
+        <v>-18.39963009738815</v>
       </c>
       <c r="F74">
-        <v>-2.360305492944668</v>
+        <v>-0.9147521879131542</v>
       </c>
       <c r="G74">
-        <v>-11.81557417831728</v>
+        <v>-12.56341805032479</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-21.5802541705764</v>
       </c>
       <c r="E75">
-        <v>-17.9085668499744</v>
+        <v>-19.07814853794804</v>
       </c>
       <c r="F75">
-        <v>-1.835770827980979</v>
+        <v>-1.007771220308316</v>
       </c>
       <c r="G75">
-        <v>-12.13953494776705</v>
+        <v>-12.59407080256906</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-21.3685599710273</v>
       </c>
       <c r="E76">
-        <v>-19.22102316073346</v>
+        <v>-18.35443485175136</v>
       </c>
       <c r="F76">
-        <v>-2.493172310884098</v>
+        <v>-0.9594343256201595</v>
       </c>
       <c r="G76">
-        <v>-13.09659475370031</v>
+        <v>-12.02349257218125</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-21.13954039601116</v>
       </c>
       <c r="E77">
-        <v>-18.64447851783209</v>
+        <v>-18.16455002998021</v>
       </c>
       <c r="F77">
-        <v>-2.156866742491137</v>
+        <v>-0.8556108971902835</v>
       </c>
       <c r="G77">
-        <v>-11.75386661916172</v>
+        <v>-11.817299880492</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.89594501375609</v>
       </c>
       <c r="E78">
-        <v>-20.37588586777191</v>
+        <v>-19.18507711671707</v>
       </c>
       <c r="F78">
-        <v>-1.975735097827594</v>
+        <v>-1.300115330634707</v>
       </c>
       <c r="G78">
-        <v>-11.20803955286997</v>
+        <v>-11.22194176781765</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.62817870601948</v>
       </c>
       <c r="E79">
-        <v>-22.02958663382419</v>
+        <v>-20.32672845853124</v>
       </c>
       <c r="F79">
-        <v>-2.504214448363415</v>
+        <v>-1.503455505367304</v>
       </c>
       <c r="G79">
-        <v>-10.58798379636367</v>
+        <v>-11.43320322013053</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-20.35941535315509</v>
       </c>
       <c r="E80">
-        <v>-20.92791825743415</v>
+        <v>-19.70652941139459</v>
       </c>
       <c r="F80">
-        <v>-2.843840113306795</v>
+        <v>-1.362928774054188</v>
       </c>
       <c r="G80">
-        <v>-10.25813188174406</v>
+        <v>-11.08877943457562</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-20.07387437197587</v>
       </c>
       <c r="E81">
-        <v>-20.76167351452391</v>
+        <v>-20.04014857069542</v>
       </c>
       <c r="F81">
-        <v>-2.018117687624429</v>
+        <v>-1.14604230718361</v>
       </c>
       <c r="G81">
-        <v>-10.49895348968982</v>
+        <v>-10.96528468855448</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.78743281205185</v>
       </c>
       <c r="E82">
-        <v>-19.85250648303967</v>
+        <v>-20.2768566969427</v>
       </c>
       <c r="F82">
-        <v>-2.328868121641024</v>
+        <v>-1.465049079103908</v>
       </c>
       <c r="G82">
-        <v>-10.46912051124717</v>
+        <v>-10.83001417905513</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.5066337921148</v>
       </c>
       <c r="E83">
-        <v>-20.65577908537476</v>
+        <v>-21.26557018493138</v>
       </c>
       <c r="F83">
-        <v>-2.57398866306862</v>
+        <v>-1.411974751239141</v>
       </c>
       <c r="G83">
-        <v>-10.86794568721941</v>
+        <v>-10.54113137393156</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-19.22070588726343</v>
       </c>
       <c r="E84">
-        <v>-22.30698792463214</v>
+        <v>-22.30782272010843</v>
       </c>
       <c r="F84">
-        <v>-2.506570325256976</v>
+        <v>-1.684802525555575</v>
       </c>
       <c r="G84">
-        <v>-10.81820055978034</v>
+        <v>-10.90518534806705</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-18.95539372039898</v>
       </c>
       <c r="E85">
-        <v>-24.43585344514673</v>
+        <v>-23.50941736097385</v>
       </c>
       <c r="F85">
-        <v>-2.483116758981514</v>
+        <v>-1.599101290796743</v>
       </c>
       <c r="G85">
-        <v>-10.73577021543282</v>
+        <v>-9.886624231800933</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.69876926005172</v>
       </c>
       <c r="E86">
-        <v>-24.00329233245451</v>
+        <v>-24.47152122400436</v>
       </c>
       <c r="F86">
-        <v>-3.065934526038773</v>
+        <v>-1.834635964639144</v>
       </c>
       <c r="G86">
-        <v>-10.90260071092185</v>
+        <v>-9.420514946226522</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.46632712706187</v>
       </c>
       <c r="E87">
-        <v>-24.68995522042239</v>
+        <v>-24.29186576172625</v>
       </c>
       <c r="F87">
-        <v>-2.778205250513379</v>
+        <v>-2.138399947980528</v>
       </c>
       <c r="G87">
-        <v>-10.63592881540717</v>
+        <v>-10.07352221558955</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.26962426122911</v>
       </c>
       <c r="E88">
-        <v>-27.61274031136855</v>
+        <v>-25.76596505724764</v>
       </c>
       <c r="F88">
-        <v>-3.387920935506942</v>
+        <v>-2.046637548935413</v>
       </c>
       <c r="G88">
-        <v>-9.737981488505898</v>
+        <v>-10.38998623194594</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-18.09731876170228</v>
       </c>
       <c r="E89">
-        <v>-26.8273223645189</v>
+        <v>-26.51774614557751</v>
       </c>
       <c r="F89">
-        <v>-2.135580185341398</v>
+        <v>-2.428444510396747</v>
       </c>
       <c r="G89">
-        <v>-9.400207269424547</v>
+        <v>-9.64910652113522</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-17.97636486690805</v>
       </c>
       <c r="E90">
-        <v>-27.61833053381177</v>
+        <v>-28.11849762044955</v>
       </c>
       <c r="F90">
-        <v>-2.620136182711178</v>
+        <v>-2.352884149382987</v>
       </c>
       <c r="G90">
-        <v>-10.7990285568755</v>
+        <v>-9.680678255475552</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-17.89482326949789</v>
       </c>
       <c r="E91">
-        <v>-29.6480921256933</v>
+        <v>-29.41657551360206</v>
       </c>
       <c r="F91">
-        <v>-3.248510015085396</v>
+        <v>-2.698189101239961</v>
       </c>
       <c r="G91">
-        <v>-9.813425480327593</v>
+        <v>-10.17470423296274</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-17.86103373570679</v>
       </c>
       <c r="E92">
-        <v>-29.72735408722199</v>
+        <v>-30.97318458190816</v>
       </c>
       <c r="F92">
-        <v>-3.994933657665169</v>
+        <v>-2.795953850485761</v>
       </c>
       <c r="G92">
-        <v>-10.42277848938262</v>
+        <v>-9.839112596359557</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-17.88171529624027</v>
       </c>
       <c r="E93">
-        <v>-31.52603100099006</v>
+        <v>-32.57001957850088</v>
       </c>
       <c r="F93">
-        <v>-3.085319979999087</v>
+        <v>-2.887467739310037</v>
       </c>
       <c r="G93">
-        <v>-10.01208617387147</v>
+        <v>-9.903406098032608</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.93479287239629</v>
       </c>
       <c r="E94">
-        <v>-32.84766798538266</v>
+        <v>-33.99508813772702</v>
       </c>
       <c r="F94">
-        <v>-2.867350008565648</v>
+        <v>-2.861667408182444</v>
       </c>
       <c r="G94">
-        <v>-9.864255372144275</v>
+        <v>-10.3870883054498</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.0375209001533</v>
       </c>
       <c r="E95">
-        <v>-35.55523781868754</v>
+        <v>-35.53730840539825</v>
       </c>
       <c r="F95">
-        <v>-3.737580614800432</v>
+        <v>-2.912621943863447</v>
       </c>
       <c r="G95">
-        <v>-11.23407128718796</v>
+        <v>-10.74056093175752</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.16652842468946</v>
       </c>
       <c r="E96">
-        <v>-38.01832056093372</v>
+        <v>-37.53304481350112</v>
       </c>
       <c r="F96">
-        <v>-3.963834260261867</v>
+        <v>-3.126504750531474</v>
       </c>
       <c r="G96">
-        <v>-10.42901425283849</v>
+        <v>-11.24689265387491</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.31400084323917</v>
       </c>
       <c r="E97">
-        <v>-41.80328740364634</v>
+        <v>-39.48804652493008</v>
       </c>
       <c r="F97">
-        <v>-3.739105639188986</v>
+        <v>-3.202966375279479</v>
       </c>
       <c r="G97">
-        <v>-11.03408433539179</v>
+        <v>-11.30275606126326</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.47196885390238</v>
       </c>
       <c r="E98">
-        <v>-42.45823636993783</v>
+        <v>-41.17842637679757</v>
       </c>
       <c r="F98">
-        <v>-4.234388994425019</v>
+        <v>-3.270736769237312</v>
       </c>
       <c r="G98">
-        <v>-11.1590554574792</v>
+        <v>-11.28528626383183</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.60537082577165</v>
       </c>
       <c r="E99">
-        <v>-44.11260995622473</v>
+        <v>-43.46195333383746</v>
       </c>
       <c r="F99">
-        <v>-4.459534284301508</v>
+        <v>-3.51285447882976</v>
       </c>
       <c r="G99">
-        <v>-10.85564777482297</v>
+        <v>-12.24664596610665</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.71543760666501</v>
       </c>
       <c r="E100">
-        <v>-44.55498303067186</v>
+        <v>-45.61156622152522</v>
       </c>
       <c r="F100">
-        <v>-4.332451955935827</v>
+        <v>-3.453855667300171</v>
       </c>
       <c r="G100">
-        <v>-10.80891283589745</v>
+        <v>-11.70533679332982</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.7775793598116</v>
       </c>
       <c r="E101">
-        <v>-46.17449975261231</v>
+        <v>-47.37693230386251</v>
       </c>
       <c r="F101">
-        <v>-4.437025056865237</v>
+        <v>-3.678708543483471</v>
       </c>
       <c r="G101">
-        <v>-11.45785125981523</v>
+        <v>-11.91982251521273</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.77251932640673</v>
       </c>
       <c r="E102">
-        <v>-48.90750489037326</v>
+        <v>-49.55715851222559</v>
       </c>
       <c r="F102">
-        <v>-4.443442419134724</v>
+        <v>-3.857925002711742</v>
       </c>
       <c r="G102">
-        <v>-11.74108571901593</v>
+        <v>-12.79507072326657</v>
       </c>
     </row>
   </sheetData>
